--- a/bnc-streamlit-app/data/points/2lzhf44ic9g2dj0l29fji2xw4_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/2lzhf44ic9g2dj0l29fji2xw4_playerlog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG33"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,106 +622,6 @@
       <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>time_off_abs</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Assists</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Key Passes</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Dribbles</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Ball Recoveries</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Clearance</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Interceptions</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Tackles</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Blocks/Saves</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Shots on Target</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Yellow Card</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Red Card</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Own Goal</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Penalty Scored</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Penalty Missed</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Penalty Saved</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>BnC Position</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>DEFCONS</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>ATTCONS</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Total Score</t>
         </is>
       </c>
     </row>
@@ -837,68 +737,6 @@
       <c r="AM2" t="n">
         <v>97</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1008,79 +846,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>0.7544718199999999</v>
+        <v>0.67671853</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>97</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1193,79 +973,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>1.08765482</v>
+        <v>1.06706455</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>+0.53</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>88</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1376,79 +1098,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>1.02072108</v>
+        <v>0.9855933100000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>+0.46</t>
+          <t>+0.52</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
         <v>97</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1559,79 +1223,21 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>1.34508738</v>
+        <v>1.28301443</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>+0.79</t>
+          <t>+0.82</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>97</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1742,79 +1348,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>0.4244325900000001</v>
+        <v>0.4129224300000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>97</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1927,79 +1475,21 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>1.36223912</v>
+        <v>1.24621615</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+0.81</t>
+          <t>+0.78</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>64</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2112,79 +1602,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.79844319</v>
+        <v>0.80638553</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>+0.24</t>
+          <t>+0.34</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
         <v>88</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2295,79 +1727,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>1.92611627</v>
+        <v>2.19234424</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+1.37</t>
+          <t>+1.73</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
         <v>97</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2480,11 +1854,11 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>1.16062357</v>
+        <v>0.9933322900000001</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>+0.53</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2495,68 +1869,6 @@
       </c>
       <c r="AM11" t="n">
         <v>65</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="BE11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2669,79 +1981,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>1.93109301</v>
+        <v>1.78499812</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>+1.38</t>
+          <t>+1.32</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
         <v>78</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2856,11 +2110,11 @@
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>-0.49582149</v>
+        <v>-0.48333805</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2871,64 +2125,6 @@
       </c>
       <c r="AM13" t="n">
         <v>97</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3047,75 +2243,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
         <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>97</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3234,75 +2372,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>88</v>
       </c>
       <c r="AM15" t="n">
         <v>97</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3421,7 +2501,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3432,64 +2512,6 @@
       </c>
       <c r="AM16" t="n">
         <v>97</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3604,79 +2626,21 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>0.33788044</v>
+        <v>0.29665433</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
         <v>78</v>
       </c>
       <c r="AM17" t="n">
         <v>97</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3791,64 +2755,6 @@
       <c r="AM18" t="n">
         <v>97</v>
       </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3964,75 +2870,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
         <v>59</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4143,79 +2991,21 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>0.7726903499999999</v>
+        <v>-0.06191255000000004</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>+0.22</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>97</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4332,7 +3122,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4343,64 +3133,6 @@
       </c>
       <c r="AM21" t="n">
         <v>78</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4521,79 +3253,21 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.7812285000000001</v>
+        <v>0.7942888</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.23</t>
+          <t>+0.33</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
         <v>97</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4714,79 +3388,21 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>1.31928265</v>
+        <v>0.18348162</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+0.76</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
         <v>97</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4899,11 +3515,11 @@
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>-0.1268534900000001</v>
+        <v>-0.12937131</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -4914,64 +3530,6 @@
       </c>
       <c r="AM24" t="n">
         <v>59</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -5092,79 +3650,21 @@
         </is>
       </c>
       <c r="AI25" t="n">
-        <v>0.90883831</v>
+        <v>0.89748056</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+0.43</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>97</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -5277,79 +3777,21 @@
         </is>
       </c>
       <c r="AI26" t="n">
-        <v>0.07546674</v>
+        <v>0.16000166</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>59</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5472,79 +3914,21 @@
         </is>
       </c>
       <c r="AI27" t="n">
-        <v>0.45863727</v>
+        <v>0.45721345</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
       </c>
       <c r="AM27" t="n">
         <v>87</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -5669,75 +4053,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
       </c>
       <c r="AM28" t="n">
         <v>97</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5856,75 +4182,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL29" t="n">
         <v>59</v>
       </c>
       <c r="AM29" t="n">
         <v>97</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -6043,7 +4311,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -6054,64 +4322,6 @@
       </c>
       <c r="AM30" t="n">
         <v>97</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="inlineStr"/>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6246,75 +4456,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
         <v>59</v>
       </c>
       <c r="AM31" t="n">
         <v>97</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6449,75 +4601,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL32" t="n">
         <v>59</v>
       </c>
       <c r="AM32" t="n">
         <v>97</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6646,7 +4740,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6657,64 +4751,6 @@
       </c>
       <c r="AM33" t="n">
         <v>97</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
